--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521375</v>
+        <v>121521372</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>79689</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561408</v>
+        <v>561355</v>
       </c>
       <c r="R2" t="n">
-        <v>7000405</v>
+        <v>7000416</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521374</v>
+        <v>121521371</v>
       </c>
       <c r="B3" t="n">
-        <v>57370</v>
+        <v>90737</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +798,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561402</v>
+        <v>561319</v>
       </c>
       <c r="R3" t="n">
-        <v>7000406</v>
+        <v>7000441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Högstubbe</t>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521372</v>
+        <v>121521378</v>
       </c>
       <c r="B4" t="n">
-        <v>79688</v>
+        <v>78608</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,34 +909,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561355</v>
+        <v>561465</v>
       </c>
       <c r="R4" t="n">
-        <v>7000416</v>
+        <v>7000393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +973,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,7 +1002,7 @@
         <v>121521373</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
+        <v>79689</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,10 +1106,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521378</v>
+        <v>121521375</v>
       </c>
       <c r="B6" t="n">
-        <v>78607</v>
+        <v>97058</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1110,42 +1118,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561465</v>
+        <v>561408</v>
       </c>
       <c r="R6" t="n">
-        <v>7000393</v>
+        <v>7000405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521377</v>
+        <v>121521374</v>
       </c>
       <c r="B7" t="n">
-        <v>97052</v>
+        <v>57371</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1244,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561440</v>
+        <v>561402</v>
       </c>
       <c r="R7" t="n">
-        <v>7000403</v>
+        <v>7000406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,6 +1284,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,7 +1318,7 @@
         <v>121521370</v>
       </c>
       <c r="B8" t="n">
-        <v>90999</v>
+        <v>91005</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1412,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521371</v>
+        <v>121521376</v>
       </c>
       <c r="B9" t="n">
-        <v>90731</v>
+        <v>79689</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,38 +1437,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561319</v>
+        <v>561433</v>
       </c>
       <c r="R9" t="n">
-        <v>7000441</v>
+        <v>7000404</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1501,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,7 +1531,7 @@
         <v>121521379</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1629,10 +1634,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521376</v>
+        <v>121521377</v>
       </c>
       <c r="B11" t="n">
-        <v>79688</v>
+        <v>97058</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,25 +1646,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561433</v>
+        <v>561440</v>
       </c>
       <c r="R11" t="n">
-        <v>7000404</v>
+        <v>7000403</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,11 +1710,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521372</v>
+        <v>121521376</v>
       </c>
       <c r="B2" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561355</v>
+        <v>561433</v>
       </c>
       <c r="R2" t="n">
-        <v>7000416</v>
+        <v>7000404</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Levande äldre asp</t>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521371</v>
+        <v>121521370</v>
       </c>
       <c r="B3" t="n">
-        <v>90737</v>
+        <v>91006</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,26 +798,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561319</v>
+        <v>561312</v>
       </c>
       <c r="R3" t="n">
-        <v>7000441</v>
+        <v>7000454</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521378</v>
+        <v>121521379</v>
       </c>
       <c r="B4" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -928,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -937,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561465</v>
+        <v>561494</v>
       </c>
       <c r="R4" t="n">
-        <v>7000393</v>
+        <v>7000427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521373</v>
+        <v>121521372</v>
       </c>
       <c r="B5" t="n">
-        <v>79689</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1039,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561366</v>
+        <v>561355</v>
       </c>
       <c r="R5" t="n">
-        <v>7000448</v>
+        <v>7000416</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1074,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre levande sälg</t>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521375</v>
+        <v>121521373</v>
       </c>
       <c r="B6" t="n">
-        <v>97058</v>
+        <v>79690</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1118,25 +1113,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561408</v>
+        <v>561366</v>
       </c>
       <c r="R6" t="n">
-        <v>7000405</v>
+        <v>7000448</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1177,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521374</v>
+        <v>121521377</v>
       </c>
       <c r="B7" t="n">
-        <v>57371</v>
+        <v>97059</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1220,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561402</v>
+        <v>561440</v>
       </c>
       <c r="R7" t="n">
-        <v>7000406</v>
+        <v>7000403</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,11 +1284,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1315,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121521370</v>
+        <v>121521375</v>
       </c>
       <c r="B8" t="n">
-        <v>91005</v>
+        <v>97059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1327,42 +1322,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561312</v>
+        <v>561408</v>
       </c>
       <c r="R8" t="n">
-        <v>7000454</v>
+        <v>7000405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1421,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521376</v>
+        <v>121521378</v>
       </c>
       <c r="B9" t="n">
-        <v>79689</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1437,34 +1428,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561433</v>
+        <v>561465</v>
       </c>
       <c r="R9" t="n">
-        <v>7000404</v>
+        <v>7000393</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,11 +1492,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521379</v>
+        <v>121521374</v>
       </c>
       <c r="B10" t="n">
-        <v>78608</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1544,38 +1534,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561494</v>
+        <v>561402</v>
       </c>
       <c r="R10" t="n">
-        <v>7000427</v>
+        <v>7000406</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,6 +1594,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521377</v>
+        <v>121521371</v>
       </c>
       <c r="B11" t="n">
-        <v>97058</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,38 +1637,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561440</v>
+        <v>561319</v>
       </c>
       <c r="R11" t="n">
-        <v>7000403</v>
+        <v>7000441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,6 +1705,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521376</v>
+        <v>121521370</v>
       </c>
       <c r="B2" t="n">
-        <v>79690</v>
+        <v>91006</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561433</v>
+        <v>561312</v>
       </c>
       <c r="R2" t="n">
-        <v>7000404</v>
+        <v>7000454</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521370</v>
+        <v>121521375</v>
       </c>
       <c r="B3" t="n">
-        <v>91006</v>
+        <v>97059</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,42 +793,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561312</v>
+        <v>561408</v>
       </c>
       <c r="R3" t="n">
-        <v>7000454</v>
+        <v>7000405</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521379</v>
+        <v>121521372</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,38 +899,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561494</v>
+        <v>561355</v>
       </c>
       <c r="R4" t="n">
-        <v>7000427</v>
+        <v>7000416</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +959,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521372</v>
+        <v>121521379</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,34 +1006,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561355</v>
+        <v>561494</v>
       </c>
       <c r="R5" t="n">
-        <v>7000416</v>
+        <v>7000427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,11 +1070,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521373</v>
+        <v>121521374</v>
       </c>
       <c r="B6" t="n">
-        <v>79690</v>
+        <v>57372</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1141,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561366</v>
+        <v>561402</v>
       </c>
       <c r="R6" t="n">
-        <v>7000448</v>
+        <v>7000406</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1181,7 +1176,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Äldre levande sälg</t>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521377</v>
+        <v>121521376</v>
       </c>
       <c r="B7" t="n">
-        <v>97059</v>
+        <v>79690</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,25 +1215,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561440</v>
+        <v>561433</v>
       </c>
       <c r="R7" t="n">
-        <v>7000403</v>
+        <v>7000404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1284,6 +1279,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121521375</v>
+        <v>121521371</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,38 +1322,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561408</v>
+        <v>561319</v>
       </c>
       <c r="R8" t="n">
-        <v>7000405</v>
+        <v>7000441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,6 +1390,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521378</v>
+        <v>121521377</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,42 +1433,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561465</v>
+        <v>561440</v>
       </c>
       <c r="R9" t="n">
-        <v>7000393</v>
+        <v>7000403</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521374</v>
+        <v>121521378</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,34 +1539,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561402</v>
+        <v>561465</v>
       </c>
       <c r="R10" t="n">
-        <v>7000406</v>
+        <v>7000393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,11 +1603,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521371</v>
+        <v>121521373</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561319</v>
+        <v>561366</v>
       </c>
       <c r="R11" t="n">
-        <v>7000441</v>
+        <v>7000448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521370</v>
+        <v>121521374</v>
       </c>
       <c r="B2" t="n">
-        <v>91006</v>
+        <v>57372</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561312</v>
+        <v>561402</v>
       </c>
       <c r="R2" t="n">
-        <v>7000454</v>
+        <v>7000406</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521375</v>
+        <v>121521376</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>79690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561408</v>
+        <v>561433</v>
       </c>
       <c r="R3" t="n">
-        <v>7000405</v>
+        <v>7000404</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521372</v>
+        <v>121521375</v>
       </c>
       <c r="B4" t="n">
-        <v>79690</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561355</v>
+        <v>561408</v>
       </c>
       <c r="R4" t="n">
-        <v>7000416</v>
+        <v>7000405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,11 +965,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521379</v>
+        <v>121521377</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,42 +1003,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561494</v>
+        <v>561440</v>
       </c>
       <c r="R5" t="n">
-        <v>7000427</v>
+        <v>7000403</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521374</v>
+        <v>121521371</v>
       </c>
       <c r="B6" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1112,34 +1109,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561402</v>
+        <v>561319</v>
       </c>
       <c r="R6" t="n">
-        <v>7000406</v>
+        <v>7000441</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1177,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Högstubbe</t>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521376</v>
+        <v>121521370</v>
       </c>
       <c r="B7" t="n">
-        <v>79690</v>
+        <v>91006</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,34 +1220,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561433</v>
+        <v>561312</v>
       </c>
       <c r="R7" t="n">
-        <v>7000404</v>
+        <v>7000454</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,11 +1284,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121521371</v>
+        <v>121521372</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>79690</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,38 +1326,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561319</v>
+        <v>561355</v>
       </c>
       <c r="R8" t="n">
-        <v>7000441</v>
+        <v>7000416</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1390,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1421,10 +1417,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521377</v>
+        <v>121521379</v>
       </c>
       <c r="B9" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,38 +1429,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561440</v>
+        <v>561494</v>
       </c>
       <c r="R9" t="n">
-        <v>7000403</v>
+        <v>7000427</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521378</v>
+        <v>121521373</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,38 +1539,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561465</v>
+        <v>561366</v>
       </c>
       <c r="R10" t="n">
-        <v>7000393</v>
+        <v>7000448</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,6 +1599,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1630,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521373</v>
+        <v>121521378</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1645,34 +1646,38 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561366</v>
+        <v>561465</v>
       </c>
       <c r="R11" t="n">
-        <v>7000448</v>
+        <v>7000393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,11 +1710,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521376</v>
+        <v>121521370</v>
       </c>
       <c r="B3" t="n">
-        <v>79690</v>
+        <v>91006</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,34 +798,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561433</v>
+        <v>561312</v>
       </c>
       <c r="R3" t="n">
-        <v>7000404</v>
+        <v>7000454</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521375</v>
+        <v>121521377</v>
       </c>
       <c r="B4" t="n">
         <v>97059</v>
@@ -929,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561408</v>
+        <v>561440</v>
       </c>
       <c r="R4" t="n">
-        <v>7000405</v>
+        <v>7000403</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521377</v>
+        <v>121521373</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>79690</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1002,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561440</v>
+        <v>561366</v>
       </c>
       <c r="R5" t="n">
-        <v>7000403</v>
+        <v>7000448</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521370</v>
+        <v>121521378</v>
       </c>
       <c r="B7" t="n">
-        <v>91006</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1220,26 +1224,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1248,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561312</v>
+        <v>561465</v>
       </c>
       <c r="R7" t="n">
-        <v>7000454</v>
+        <v>7000393</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,10 +1314,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121521372</v>
+        <v>121521375</v>
       </c>
       <c r="B8" t="n">
-        <v>79690</v>
+        <v>97059</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,25 +1326,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1354,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561355</v>
+        <v>561408</v>
       </c>
       <c r="R8" t="n">
-        <v>7000416</v>
+        <v>7000405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,11 +1390,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521379</v>
+        <v>121521376</v>
       </c>
       <c r="B9" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1433,38 +1432,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561494</v>
+        <v>561433</v>
       </c>
       <c r="R9" t="n">
-        <v>7000427</v>
+        <v>7000404</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1497,6 +1492,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,7 +1523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521373</v>
+        <v>121521372</v>
       </c>
       <c r="B10" t="n">
         <v>79690</v>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561366</v>
+        <v>561355</v>
       </c>
       <c r="R10" t="n">
-        <v>7000448</v>
+        <v>7000416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre levande sälg</t>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,7 +1630,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521378</v>
+        <v>121521379</v>
       </c>
       <c r="B11" t="n">
         <v>78609</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561465</v>
+        <v>561494</v>
       </c>
       <c r="R11" t="n">
-        <v>7000393</v>
+        <v>7000427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -1523,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521372</v>
+        <v>121521379</v>
       </c>
       <c r="B10" t="n">
-        <v>79690</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,34 +1539,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561355</v>
+        <v>561494</v>
       </c>
       <c r="R10" t="n">
-        <v>7000416</v>
+        <v>7000427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1599,11 +1603,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1630,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521379</v>
+        <v>121521372</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>79690</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1646,38 +1645,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561494</v>
+        <v>561355</v>
       </c>
       <c r="R11" t="n">
-        <v>7000427</v>
+        <v>7000416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,6 +1705,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521374</v>
+        <v>121521370</v>
       </c>
       <c r="B2" t="n">
-        <v>57372</v>
+        <v>91014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561402</v>
+        <v>561312</v>
       </c>
       <c r="R2" t="n">
-        <v>7000406</v>
+        <v>7000454</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521370</v>
+        <v>121521379</v>
       </c>
       <c r="B3" t="n">
-        <v>91006</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -826,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561312</v>
+        <v>561494</v>
       </c>
       <c r="R3" t="n">
-        <v>7000454</v>
+        <v>7000427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -891,7 +890,7 @@
         <v>121521377</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -990,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521373</v>
+        <v>121521376</v>
       </c>
       <c r="B5" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561366</v>
+        <v>561433</v>
       </c>
       <c r="R5" t="n">
-        <v>7000448</v>
+        <v>7000404</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,7 +1069,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Äldre levande sälg</t>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,10 +1096,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521371</v>
+        <v>121521378</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,26 +1112,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1141,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561319</v>
+        <v>561465</v>
       </c>
       <c r="R6" t="n">
-        <v>7000441</v>
+        <v>7000393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,11 +1176,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,10 +1202,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521378</v>
+        <v>121521371</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,26 +1218,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1252,10 +1246,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561465</v>
+        <v>561319</v>
       </c>
       <c r="R7" t="n">
-        <v>7000393</v>
+        <v>7000441</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,6 +1282,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1316,7 @@
         <v>121521375</v>
       </c>
       <c r="B8" t="n">
-        <v>97059</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1416,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521376</v>
+        <v>121521374</v>
       </c>
       <c r="B9" t="n">
-        <v>79690</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1456,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561433</v>
+        <v>561402</v>
       </c>
       <c r="R9" t="n">
-        <v>7000404</v>
+        <v>7000406</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1495,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gammal levande sälg</t>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521379</v>
+        <v>121521372</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,38 +1538,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561494</v>
+        <v>561355</v>
       </c>
       <c r="R10" t="n">
-        <v>7000427</v>
+        <v>7000416</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,6 +1598,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521372</v>
+        <v>121521373</v>
       </c>
       <c r="B11" t="n">
-        <v>79690</v>
+        <v>79697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561355</v>
+        <v>561366</v>
       </c>
       <c r="R11" t="n">
-        <v>7000416</v>
+        <v>7000448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Levande äldre asp</t>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -1415,10 +1415,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521374</v>
+        <v>121521372</v>
       </c>
       <c r="B9" t="n">
-        <v>57373</v>
+        <v>79697</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1431,21 +1431,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1455,10 +1455,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561402</v>
+        <v>561355</v>
       </c>
       <c r="R9" t="n">
-        <v>7000406</v>
+        <v>7000416</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Högstubbe</t>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1522,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521372</v>
+        <v>121521374</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,21 +1538,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561355</v>
+        <v>561402</v>
       </c>
       <c r="R10" t="n">
-        <v>7000416</v>
+        <v>7000406</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Levande äldre asp</t>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521377</v>
+        <v>121521372</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>79697</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561440</v>
+        <v>561355</v>
       </c>
       <c r="R3" t="n">
-        <v>7000403</v>
+        <v>7000416</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521376</v>
+        <v>121521370</v>
       </c>
       <c r="B4" t="n">
-        <v>79697</v>
+        <v>91014</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,34 +900,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561433</v>
+        <v>561312</v>
       </c>
       <c r="R4" t="n">
-        <v>7000404</v>
+        <v>7000454</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +964,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521374</v>
+        <v>121521371</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,34 +1006,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561402</v>
+        <v>561319</v>
       </c>
       <c r="R5" t="n">
-        <v>7000406</v>
+        <v>7000441</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1074,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Högstubbe</t>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521371</v>
+        <v>121521377</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>97067</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,42 +1113,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561319</v>
+        <v>561440</v>
       </c>
       <c r="R6" t="n">
-        <v>7000441</v>
+        <v>7000403</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,11 +1177,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Låga</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121521373</v>
+        <v>121521374</v>
       </c>
       <c r="B8" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,21 +1325,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1349,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561366</v>
+        <v>561402</v>
       </c>
       <c r="R8" t="n">
-        <v>7000448</v>
+        <v>7000406</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,7 +1389,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre levande sälg</t>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521370</v>
+        <v>121521376</v>
       </c>
       <c r="B10" t="n">
-        <v>91014</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,38 +1538,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561312</v>
+        <v>561433</v>
       </c>
       <c r="R10" t="n">
-        <v>7000454</v>
+        <v>7000404</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,6 +1598,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521372</v>
+        <v>121521373</v>
       </c>
       <c r="B11" t="n">
         <v>79697</v>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561355</v>
+        <v>561366</v>
       </c>
       <c r="R11" t="n">
-        <v>7000416</v>
+        <v>7000448</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Levande äldre asp</t>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521375</v>
+        <v>121521374</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561408</v>
+        <v>561402</v>
       </c>
       <c r="R2" t="n">
-        <v>7000405</v>
+        <v>7000406</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521372</v>
+        <v>121521377</v>
       </c>
       <c r="B3" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561355</v>
+        <v>561440</v>
       </c>
       <c r="R3" t="n">
-        <v>7000416</v>
+        <v>7000403</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521370</v>
+        <v>121521376</v>
       </c>
       <c r="B4" t="n">
-        <v>91014</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,38 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561312</v>
+        <v>561433</v>
       </c>
       <c r="R4" t="n">
-        <v>7000454</v>
+        <v>7000404</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521371</v>
+        <v>121521379</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1006,26 +1007,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1034,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561319</v>
+        <v>561494</v>
       </c>
       <c r="R5" t="n">
-        <v>7000441</v>
+        <v>7000427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1070,11 +1071,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Låga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521377</v>
+        <v>121521375</v>
       </c>
       <c r="B6" t="n">
         <v>97067</v>
@@ -1141,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561440</v>
+        <v>561408</v>
       </c>
       <c r="R6" t="n">
-        <v>7000403</v>
+        <v>7000405</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521379</v>
+        <v>121521373</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,38 +1215,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561494</v>
+        <v>561366</v>
       </c>
       <c r="R7" t="n">
-        <v>7000427</v>
+        <v>7000448</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1283,6 +1275,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,10 +1306,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121521374</v>
+        <v>121521371</v>
       </c>
       <c r="B8" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,34 +1322,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561402</v>
+        <v>561319</v>
       </c>
       <c r="R8" t="n">
-        <v>7000406</v>
+        <v>7000441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1390,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Högstubbe</t>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1522,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521376</v>
+        <v>121521370</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>91014</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1538,34 +1539,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561433</v>
+        <v>561312</v>
       </c>
       <c r="R10" t="n">
-        <v>7000404</v>
+        <v>7000454</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,11 +1603,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521373</v>
+        <v>121521372</v>
       </c>
       <c r="B11" t="n">
         <v>79697</v>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561366</v>
+        <v>561355</v>
       </c>
       <c r="R11" t="n">
-        <v>7000448</v>
+        <v>7000416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Äldre levande sälg</t>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521374</v>
+        <v>121521379</v>
       </c>
       <c r="B2" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561402</v>
+        <v>561494</v>
       </c>
       <c r="R2" t="n">
-        <v>7000406</v>
+        <v>7000427</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +755,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521377</v>
+        <v>121521378</v>
       </c>
       <c r="B3" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,38 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561440</v>
+        <v>561465</v>
       </c>
       <c r="R3" t="n">
-        <v>7000403</v>
+        <v>7000393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521376</v>
+        <v>121521375</v>
       </c>
       <c r="B4" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561433</v>
+        <v>561408</v>
       </c>
       <c r="R4" t="n">
-        <v>7000404</v>
+        <v>7000405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521379</v>
+        <v>121521370</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>91014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,26 +1005,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1035,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561494</v>
+        <v>561312</v>
       </c>
       <c r="R5" t="n">
-        <v>7000427</v>
+        <v>7000454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521375</v>
+        <v>121521374</v>
       </c>
       <c r="B6" t="n">
-        <v>97067</v>
+        <v>57373</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,25 +1107,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561408</v>
+        <v>561402</v>
       </c>
       <c r="R6" t="n">
-        <v>7000405</v>
+        <v>7000406</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,6 +1171,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1199,7 +1202,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521373</v>
+        <v>121521372</v>
       </c>
       <c r="B7" t="n">
         <v>79697</v>
@@ -1239,10 +1242,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561366</v>
+        <v>561355</v>
       </c>
       <c r="R7" t="n">
-        <v>7000448</v>
+        <v>7000416</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1279,7 +1282,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Äldre levande sälg</t>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1306,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121521371</v>
+        <v>121521373</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>79697</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,38 +1325,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561319</v>
+        <v>561366</v>
       </c>
       <c r="R8" t="n">
-        <v>7000441</v>
+        <v>7000448</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,7 +1389,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521378</v>
+        <v>121521377</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1429,42 +1428,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561465</v>
+        <v>561440</v>
       </c>
       <c r="R9" t="n">
-        <v>7000393</v>
+        <v>7000403</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1518,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521370</v>
+        <v>121521371</v>
       </c>
       <c r="B10" t="n">
-        <v>91014</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1539,26 +1534,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1567,10 +1562,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561312</v>
+        <v>561319</v>
       </c>
       <c r="R10" t="n">
-        <v>7000454</v>
+        <v>7000441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,6 +1598,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521372</v>
+        <v>121521376</v>
       </c>
       <c r="B11" t="n">
         <v>79697</v>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561355</v>
+        <v>561433</v>
       </c>
       <c r="R11" t="n">
-        <v>7000416</v>
+        <v>7000404</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Levande äldre asp</t>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521379</v>
+        <v>121521370</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>91014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561494</v>
+        <v>561312</v>
       </c>
       <c r="R2" t="n">
-        <v>7000427</v>
+        <v>7000454</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121521378</v>
+        <v>121521371</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561465</v>
+        <v>561319</v>
       </c>
       <c r="R3" t="n">
-        <v>7000393</v>
+        <v>7000441</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,6 +861,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Låga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521375</v>
+        <v>121521378</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,38 +904,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561408</v>
+        <v>561465</v>
       </c>
       <c r="R4" t="n">
-        <v>7000405</v>
+        <v>7000393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521370</v>
+        <v>121521374</v>
       </c>
       <c r="B5" t="n">
-        <v>91014</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1014,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561312</v>
+        <v>561402</v>
       </c>
       <c r="R5" t="n">
-        <v>7000454</v>
+        <v>7000406</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121521374</v>
+        <v>121521379</v>
       </c>
       <c r="B6" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,34 +1121,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561402</v>
+        <v>561494</v>
       </c>
       <c r="R6" t="n">
-        <v>7000406</v>
+        <v>7000427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1171,11 +1185,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1202,7 +1211,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521372</v>
+        <v>121521376</v>
       </c>
       <c r="B7" t="n">
         <v>79697</v>
@@ -1242,10 +1251,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561355</v>
+        <v>561433</v>
       </c>
       <c r="R7" t="n">
-        <v>7000416</v>
+        <v>7000404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1282,7 +1291,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Levande äldre asp</t>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,10 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121521373</v>
+        <v>121521375</v>
       </c>
       <c r="B8" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,25 +1330,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1349,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561366</v>
+        <v>561408</v>
       </c>
       <c r="R8" t="n">
-        <v>7000448</v>
+        <v>7000405</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1385,11 +1394,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,10 +1522,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521371</v>
+        <v>121521373</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>79697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,38 +1538,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561319</v>
+        <v>561366</v>
       </c>
       <c r="R10" t="n">
-        <v>7000441</v>
+        <v>7000448</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Låga</t>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121521376</v>
+        <v>121521372</v>
       </c>
       <c r="B11" t="n">
         <v>79697</v>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561433</v>
+        <v>561355</v>
       </c>
       <c r="R11" t="n">
-        <v>7000404</v>
+        <v>7000416</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Gammal levande sälg</t>
+          <t>Levande äldre asp</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 37858-2024 artfynd.xlsx
+++ b/artfynd/A 37858-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121521370</v>
+        <v>121521373</v>
       </c>
       <c r="B2" t="n">
-        <v>91014</v>
+        <v>79697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561312</v>
+        <v>561366</v>
       </c>
       <c r="R2" t="n">
-        <v>7000454</v>
+        <v>7000448</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -892,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121521378</v>
+        <v>121521376</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>79697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,38 +909,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561465</v>
+        <v>561433</v>
       </c>
       <c r="R4" t="n">
-        <v>7000393</v>
+        <v>7000404</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,6 +969,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gammal levande sälg</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1000,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121521374</v>
+        <v>121521370</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>91014</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,34 +1016,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561402</v>
+        <v>561312</v>
       </c>
       <c r="R5" t="n">
-        <v>7000406</v>
+        <v>7000454</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1080,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1211,10 +1212,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121521376</v>
+        <v>121521374</v>
       </c>
       <c r="B7" t="n">
-        <v>79697</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,21 +1228,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,10 +1252,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561433</v>
+        <v>561402</v>
       </c>
       <c r="R7" t="n">
-        <v>7000404</v>
+        <v>7000406</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,7 +1292,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gammal levande sälg</t>
+          <t>Högstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,10 +1421,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121521377</v>
+        <v>121521378</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1432,38 +1433,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stadsforsen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561440</v>
+        <v>561465</v>
       </c>
       <c r="R9" t="n">
-        <v>7000403</v>
+        <v>7000393</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1522,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121521373</v>
+        <v>121521377</v>
       </c>
       <c r="B10" t="n">
-        <v>79697</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1534,25 +1539,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1562,10 +1567,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561366</v>
+        <v>561440</v>
       </c>
       <c r="R10" t="n">
-        <v>7000448</v>
+        <v>7000403</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,11 +1603,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre levande sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
